--- a/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
+++ b/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">

--- a/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
+++ b/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">

--- a/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
+++ b/docs/06_Dynamic_Fuzzing/fuzzing_campaigns.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
